--- a/data/trans_orig/IP31KM02_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_R_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92149</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>82810</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100379</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>74,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>80691</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72428</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>87712</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>103220</t>
+          <t>83625</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>74540</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111929</t>
+          <t>91210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>175774</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170033</t>
+          <t>163275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197221</t>
+          <t>187973</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22517</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40086</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>33560</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26539</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41823</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,37%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44336</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>67155</t>
+          <t>65720</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>53521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81033</t>
+          <t>78219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>169960</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>156289</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>182518</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>123922</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>109549</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>135135</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>66,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>72,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>125144</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>161412</t>
+          <t>114272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191565</t>
+          <t>135755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>301622</t>
+          <t>295104</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281425</t>
+          <t>275266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319973</t>
+          <t>309770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>75,22%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61281</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48723</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74952</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>62192</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50979</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>76565</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>55449</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55955</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86108</t>
+          <t>66321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>132012</t>
+          <t>116729</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113661</t>
+          <t>102063</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152209</t>
+          <t>136567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>92339</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79494</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>105032</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,74%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>93821</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55762</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115016</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>49,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100904</t>
+          <t>87455</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86285</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113799</t>
+          <t>97606</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>194726</t>
+          <t>179794</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146262</t>
+          <t>163389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220071</t>
+          <t>197889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94428</t>
+          <t>74183</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73233</t>
+          <t>61490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132487</t>
+          <t>87028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82185</t>
+          <t>67583</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69290</t>
+          <t>57432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96804</t>
+          <t>79845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>176613</t>
+          <t>141766</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151268</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225077</t>
+          <t>158171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>105582</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95243</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115646</t>
+          <t>115702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>110662</t>
+          <t>104968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98525</t>
+          <t>94850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122080</t>
+          <t>116613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>216245</t>
+          <t>209523</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200050</t>
+          <t>194261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230445</t>
+          <t>224112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50463</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71923</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>37,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>58937</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>48873</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>69276</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66647</t>
+          <t>59011</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55229</t>
+          <t>47366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78784</t>
+          <t>69129</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>125583</t>
+          <t>120621</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111383</t>
+          <t>106032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141778</t>
+          <t>135883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>459003</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>435647</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>481165</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>70,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>594</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>404017</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>349862</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>434069</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,57%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>462686</t>
+          <t>380651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>516775</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>839638</t>
+          <t>828113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>934115</t>
+          <t>890164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>227821</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>205659</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>251177</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>249117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>219065</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>303272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>252246</t>
+          <t>217015</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>227958</t>
+          <t>197766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282047</t>
+          <t>237557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>501363</t>
+          <t>444836</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>463752</t>
+          <t>414867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558229</t>
+          <t>476918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
